--- a/Planilhas_importação/Importacao_clientes.xlsx
+++ b/Planilhas_importação/Importacao_clientes.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -186,7 +186,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -211,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -225,7 +225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -239,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0">
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -251,7 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0">
+    <comment ref="T1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -263,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0">
+    <comment ref="U1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -276,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0">
+    <comment ref="V1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -288,7 +288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0">
+    <comment ref="X1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -300,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0">
+    <comment ref="Y1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -312,7 +312,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0">
+    <comment ref="Z1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -324,7 +324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0">
+    <comment ref="AA1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -336,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0">
+    <comment ref="AB1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -348,7 +348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0">
+    <comment ref="AC1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -360,7 +360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0">
+    <comment ref="AD1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -372,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0">
+    <comment ref="AE1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -385,7 +385,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0">
+    <comment ref="AF1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -397,7 +397,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0">
+    <comment ref="AG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -409,7 +409,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0">
+    <comment ref="AH1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -422,7 +422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0">
+    <comment ref="AI1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -440,7 +440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI1" authorId="0">
+    <comment ref="AJ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -452,7 +452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0">
+    <comment ref="AK1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -464,7 +464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK1" authorId="0">
+    <comment ref="AL1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -477,7 +477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL1" authorId="0">
+    <comment ref="AM1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -490,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AM1" authorId="0">
+    <comment ref="AN1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -502,7 +502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN1" authorId="0">
+    <comment ref="AO1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -517,7 +517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0">
+    <comment ref="AP1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -531,7 +531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AP1" authorId="0">
+    <comment ref="AQ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -543,7 +543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ1" authorId="0">
+    <comment ref="AR1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -555,7 +555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AR1" authorId="0">
+    <comment ref="AS1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -567,7 +567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AS1" authorId="0">
+    <comment ref="AT1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -579,7 +579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AT1" authorId="0">
+    <comment ref="AU1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -591,7 +591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AU1" authorId="0">
+    <comment ref="AV1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -603,7 +603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AV1" authorId="0">
+    <comment ref="AW1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -616,7 +616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AW1" authorId="0">
+    <comment ref="AX1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -628,7 +628,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AX1" authorId="0">
+    <comment ref="AY1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -642,7 +642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY1" authorId="0">
+    <comment ref="AZ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -654,7 +654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0">
+    <comment ref="BA1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -666,7 +666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA1" authorId="0">
+    <comment ref="BB1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -678,7 +678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BB1" authorId="0">
+    <comment ref="BC1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -691,7 +691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BC1" authorId="0">
+    <comment ref="BD1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -703,7 +703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BD1" authorId="0">
+    <comment ref="BE1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -715,7 +715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BE1" authorId="0">
+    <comment ref="BF1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -730,7 +730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BF1" authorId="0">
+    <comment ref="BG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -742,7 +742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BG1" authorId="0">
+    <comment ref="BH1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -760,7 +760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BH1" authorId="0">
+    <comment ref="BI1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -772,7 +772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BI1" authorId="0">
+    <comment ref="BJ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -784,7 +784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BJ1" authorId="0">
+    <comment ref="BK1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -796,7 +796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BK1" authorId="0">
+    <comment ref="BL1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -808,7 +808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BL1" authorId="0">
+    <comment ref="BM1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -825,7 +825,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t xml:space="preserve">cliente_cpfcnpj</t>
   </si>
@@ -864,6 +864,9 @@
   </si>
   <si>
     <t xml:space="preserve">cliente_doc_identificacao_numero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente_doc_identificacao_tipo </t>
   </si>
   <si>
     <t xml:space="preserve">cliente_doc_identificacao_emissor</t>
@@ -1363,8 +1366,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BL1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BM1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.46"/>
@@ -1379,58 +1382,58 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="28.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="29.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="12.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="19.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="22.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="20.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="26.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="23.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="22.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="21.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="18.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="28.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="17.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="30.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="27.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="33.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="29.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="25.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="24.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="35.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="38.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="39.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="20.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="27.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="30.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="19.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="22.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="28.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="25.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="27.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="24.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="20.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="20.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="1" width="21.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="23.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="26.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="30.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="1" width="23.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="38.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="1" width="34.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="29.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="1" width="40.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="1" width="43.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="44.17"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="62" min="62" style="1" width="25.74"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="63" style="1" width="32.35"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="64" min="64" style="1" width="35.6"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="75" min="65" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="29.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="12.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="19.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="20.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="26.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="23.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="22.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="28.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="17.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="30.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="27.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="33.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="29.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="25.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="24.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="35.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="38.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="39.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="20.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="27.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="30.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="19.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="22.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="28.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="25.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="27.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="24.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="20.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="1" width="20.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="21.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="23.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="26.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="1" width="30.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="25.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="1" width="38.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="34.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="1" width="29.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="1" width="40.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="43.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="1" width="44.17"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="63" style="1" width="25.74"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="64" min="64" style="1" width="32.35"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="65" min="65" style="1" width="35.6"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="76" min="66" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1479,7 +1482,7 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
@@ -1488,7 +1491,7 @@
       <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="3" t="s">
@@ -1587,7 +1590,7 @@
       <c r="AY1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="4" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
       <c r="BA1" s="4" t="s">
@@ -1605,10 +1608,10 @@
       <c r="BE1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BF1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="4" t="s">
+      <c r="BG1" s="3" t="s">
         <v>58</v>
       </c>
       <c r="BH1" s="4" t="s">
@@ -1617,7 +1620,7 @@
       <c r="BI1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BJ1" s="4" t="s">
         <v>61</v>
       </c>
       <c r="BK1" s="3" t="s">
@@ -1625,6 +1628,9 @@
       </c>
       <c r="BL1" s="3" t="s">
         <v>63</v>
+      </c>
+      <c r="BM1" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Planilhas_importação/Importacao_clientes.xlsx
+++ b/Planilhas_importação/Importacao_clientes.xlsx
@@ -130,10 +130,10 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">- Solteiro(a)
-- Divorciado(a)
-- Viúvo(a)
-- Casado(a)</t>
+          <t xml:space="preserve">- SOLTEIRO(A)
+- DIVORCIADO(A)
+- VIUVO(A)
+- CASADO(A)</t>
         </r>
       </text>
     </comment>
@@ -186,6 +186,24 @@
         </r>
       </text>
     </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Opcional. Informar se o cliente for pessoa jurídica. Informe o tipo de documento de identificação utilizado:
+- RG
+- RNE
+- RNM
+- CTPS
+- PASSAPORTE
+- CNH</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="O1" authorId="0">
       <text>
         <r>
@@ -220,8 +238,10 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informe o tipo de telefone para contato com o cliente:
-- Celular
-- Fixo</t>
+- CELULAR
+- FIXO
+- COMERCIAL
+-RESIDENCIAL</t>
         </r>
       </text>
     </comment>
@@ -247,7 +267,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obrigatório informar o CEP referente ao endereço do cliente para geração do boleto.</t>
+          <t xml:space="preserve">Obrigatório. Informar o CEP referente ao endereço do cliente para geração do boleto.
+</t>
         </r>
       </text>
     </comment>
@@ -435,7 +456,7 @@
 - RNE
 - RNM
 - CTPS
-- Passaporte
+- PASSAPORTE
 - CNH</t>
         </r>
       </text>
@@ -485,8 +506,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">- Celular
-- Fixo</t>
+          <t xml:space="preserve">Opcional. Informar o tipo do telefone:
+- CELULAR
+- FIXO
+- COMERCIAL
+-RESIDENCIAL</t>
         </r>
       </text>
     </comment>
@@ -525,9 +549,10 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">- Separação total de bens
-- Comunhão parcial de bens
-- Comunhão universal de bens</t>
+          <t xml:space="preserve">- SEPARACAO TOTAL DE BENS
+- COMUNHAO PARCIAL DE BENS
+- COMUNHAO UNIVERSAL DE BENS
+</t>
         </r>
       </text>
     </comment>
@@ -750,12 +775,12 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Informe o tipo de documento de identificação utilizado:
+          <t xml:space="preserve">Informe o tipo de documento de identificação:
 - RG
 - RNE
 - RNM
 - CTPS
-- Passaporte
+- PASSAPORTE
 - CNH</t>
         </r>
       </text>
@@ -1073,14 +1098,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFA6"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor rgb="FF00CCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1093,7 +1118,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="31">
+  <cellStyleXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1150,6 +1175,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -1160,20 +1191,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="32" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="17">
+  <cellStyles count="19">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
@@ -1191,6 +1222,8 @@
     <cellStyle name="Normal" xfId="28"/>
     <cellStyle name="Título de tabela" xfId="29"/>
     <cellStyle name="Índice" xfId="30"/>
+    <cellStyle name="caption" xfId="31"/>
+    <cellStyle name="Destaque 3" xfId="32"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -1217,7 +1250,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1229,13 +1262,13 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFFA6"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF34B3FB"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
@@ -1436,200 +1469,200 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="76" min="66" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AT1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AU1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AW1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AX1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AY1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="AZ1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="4" t="s">
+      <c r="BA1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="4" t="s">
+      <c r="BB1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="4" t="s">
+      <c r="BC1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="4" t="s">
+      <c r="BD1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="4" t="s">
+      <c r="BE1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="4" t="s">
+      <c r="BF1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BG1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="4" t="s">
+      <c r="BH1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="4" t="s">
+      <c r="BI1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="4" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BK1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BL1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BM1" s="4" t="s">
         <v>64</v>
       </c>
     </row>

--- a/Planilhas_importação/Importacao_clientes.xlsx
+++ b/Planilhas_importação/Importacao_clientes.xlsx
@@ -891,7 +891,7 @@
     <t xml:space="preserve">cliente_doc_identificacao_numero</t>
   </si>
   <si>
-    <t xml:space="preserve">cliente_doc_identificacao_tipo </t>
+    <t xml:space="preserve">cliente_doc_identificacao_tipo</t>
   </si>
   <si>
     <t xml:space="preserve">cliente_doc_identificacao_emissor</t>
@@ -1191,7 +1191,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="32" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="32" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1213,16 +1213,16 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="Body Text" xfId="20"/>
     <cellStyle name="Caption" xfId="21"/>
-    <cellStyle name="Caracteres de nota de fim" xfId="22"/>
-    <cellStyle name="Caracteres de nota de rodapé" xfId="23"/>
-    <cellStyle name="Conteúdo da lista" xfId="24"/>
-    <cellStyle name="Conteúdo da tabela" xfId="25"/>
-    <cellStyle name="FollowedHyperlink" xfId="26"/>
-    <cellStyle name="List" xfId="27"/>
-    <cellStyle name="Normal" xfId="28"/>
-    <cellStyle name="Título de tabela" xfId="29"/>
-    <cellStyle name="Índice" xfId="30"/>
-    <cellStyle name="caption" xfId="31"/>
+    <cellStyle name="caption 1" xfId="22"/>
+    <cellStyle name="Caracteres de nota de fim" xfId="23"/>
+    <cellStyle name="Caracteres de nota de rodapé" xfId="24"/>
+    <cellStyle name="Conteúdo da lista" xfId="25"/>
+    <cellStyle name="Conteúdo da tabela" xfId="26"/>
+    <cellStyle name="FollowedHyperlink" xfId="27"/>
+    <cellStyle name="List" xfId="28"/>
+    <cellStyle name="Normal" xfId="29"/>
+    <cellStyle name="Título de tabela" xfId="30"/>
+    <cellStyle name="Índice" xfId="31"/>
     <cellStyle name="Destaque 3" xfId="32"/>
   </cellStyles>
   <colors>

--- a/Planilhas_importação/Importacao_clientes.xlsx
+++ b/Planilhas_importação/Importacao_clientes.xlsx
@@ -266,13 +266,45 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Obrigatório. Informe o tipo de telefone para contato com o cliente:
+- CELULAR
+- FIXO
+- COMERCIAL
+-RESIDENCIAL</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Obrigatório. Informar utilizando o padrão a seguir:
+Celular: 5573999341121
+Telefone fixo: 557330130001</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar o CEP referente ao endereço do cliente para geração do boleto.
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0">
+    <comment ref="X1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -284,7 +316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0">
+    <comment ref="Y1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -297,7 +329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0">
+    <comment ref="Z1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -309,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0">
+    <comment ref="AB1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -321,7 +353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0">
+    <comment ref="AC1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -333,7 +365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0">
+    <comment ref="AD1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -345,7 +377,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0">
+    <comment ref="AE1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -357,7 +389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0">
+    <comment ref="AF1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -369,7 +401,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0">
+    <comment ref="AG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -381,7 +413,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0">
+    <comment ref="AH1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -393,7 +425,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0">
+    <comment ref="AI1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -406,7 +438,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0">
+    <comment ref="AJ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -418,7 +450,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0">
+    <comment ref="AK1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -430,7 +462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0">
+    <comment ref="AL1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -443,7 +475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI1" authorId="0">
+    <comment ref="AM1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -461,7 +493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0">
+    <comment ref="AN1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -473,7 +505,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK1" authorId="0">
+    <comment ref="AO1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -485,7 +517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL1" authorId="0">
+    <comment ref="AP1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -498,7 +530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AM1" authorId="0">
+    <comment ref="AQ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -514,7 +546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN1" authorId="0">
+    <comment ref="AR1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -526,7 +558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0">
+    <comment ref="AS1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -541,7 +573,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AP1" authorId="0">
+    <comment ref="AT1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -556,7 +588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ1" authorId="0">
+    <comment ref="AU1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -568,7 +600,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AR1" authorId="0">
+    <comment ref="AV1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -580,7 +612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AS1" authorId="0">
+    <comment ref="AW1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -592,7 +624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AT1" authorId="0">
+    <comment ref="AX1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -604,7 +636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AU1" authorId="0">
+    <comment ref="AY1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -616,7 +648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AV1" authorId="0">
+    <comment ref="AZ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -628,7 +660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AW1" authorId="0">
+    <comment ref="BA1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -641,7 +673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AX1" authorId="0">
+    <comment ref="BB1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -653,7 +685,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY1" authorId="0">
+    <comment ref="BC1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -667,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0">
+    <comment ref="BD1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -679,7 +711,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA1" authorId="0">
+    <comment ref="BE1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -691,7 +723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BB1" authorId="0">
+    <comment ref="BF1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -703,7 +735,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BC1" authorId="0">
+    <comment ref="BG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -716,7 +748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BD1" authorId="0">
+    <comment ref="BH1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -728,7 +760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BE1" authorId="0">
+    <comment ref="BI1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -740,7 +772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BF1" authorId="0">
+    <comment ref="BJ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -755,7 +787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BG1" authorId="0">
+    <comment ref="BK1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -767,7 +799,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BH1" authorId="0">
+    <comment ref="BL1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -785,7 +817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BI1" authorId="0">
+    <comment ref="BM1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -797,7 +829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BJ1" authorId="0">
+    <comment ref="BN1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -809,7 +841,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BK1" authorId="0">
+    <comment ref="BO1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -821,7 +853,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BL1" authorId="0">
+    <comment ref="BP1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -833,7 +865,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BM1" authorId="0">
+    <comment ref="BQ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -850,7 +882,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t xml:space="preserve">cliente_cpfcnpj</t>
   </si>
@@ -900,10 +932,22 @@
     <t xml:space="preserve">cliente_email</t>
   </si>
   <si>
-    <t xml:space="preserve">cliente_telefone_tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cliente_telefone_numero</t>
+    <t xml:space="preserve">cliente_telefone_tipo_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente_telefone_numero_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente_telefone_tipo_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente_telefone_numero_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente_telefone_tipo_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente_telefone_numero_3</t>
   </si>
   <si>
     <t xml:space="preserve">cliente_endereco_cep</t>
@@ -1054,7 +1098,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1082,6 +1126,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1182,7 +1233,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1200,6 +1251,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1399,77 +1454,82 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM1"/>
+  <dimension ref="A1:BQ1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="21.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="28.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="29.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="30.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="27.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="30.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="12.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="19.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="20.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="26.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="23.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="22.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="21.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="28.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="17.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="30.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="27.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="33.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="29.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="25.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="24.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="35.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="38.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="39.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="20.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="27.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="30.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="19.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="22.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="28.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="25.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="27.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="24.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="20.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="1" width="20.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="21.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="23.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="26.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="1" width="30.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="23.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="1" width="38.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="34.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="1" width="29.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="1" width="40.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="43.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="1" width="44.17"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="63" style="1" width="25.74"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="64" min="64" style="1" width="32.35"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="65" min="65" style="1" width="35.6"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="76" min="66" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="24.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="24.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="24.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="19.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="26.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="23.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="22.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="18.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="28.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="17.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="30.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="27.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="33.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="29.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="25.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="24.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="35.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="38.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="39.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="20.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="27.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="30.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="19.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="22.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="28.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="1" width="25.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="27.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="24.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="20.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="1" width="20.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="21.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="23.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="26.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="30.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="1" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="25.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="1" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="1" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="38.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="1" width="34.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="1" width="29.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="40.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="43.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="44.17"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="67" min="67" style="1" width="25.74"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="68" min="68" style="1" width="32.35"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="69" min="69" style="1" width="35.6"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="80" min="70" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1518,25 +1578,25 @@
       <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="4" t="s">
@@ -1626,16 +1686,16 @@
       <c r="AZ1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BB1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BC1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BD1" s="4" t="s">
         <v>55</v>
       </c>
       <c r="BE1" s="3" t="s">
@@ -1644,7 +1704,7 @@
       <c r="BF1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="4" t="s">
+      <c r="BG1" s="3" t="s">
         <v>58</v>
       </c>
       <c r="BH1" s="3" t="s">
@@ -1659,11 +1719,23 @@
       <c r="BK1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="4" t="s">
+      <c r="BL1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="4" t="s">
+      <c r="BM1" s="3" t="s">
         <v>64</v>
+      </c>
+      <c r="BN1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Planilhas_importação/Importacao_clientes.xlsx
+++ b/Planilhas_importação/Importacao_clientes.xlsx
@@ -266,7 +266,6 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informe o tipo de telefone para contato com o cliente:
 - CELULAR
@@ -283,7 +282,6 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar utilizando o padrão a seguir:
 Celular: 5573999341121
@@ -1133,6 +1131,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1140,7 +1139,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1157,6 +1156,12 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
         <bgColor rgb="FF00CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1233,7 +1238,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1255,6 +1260,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1584,19 +1597,19 @@
       <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="4" t="s">

--- a/Planilhas_importação/Importacao_clientes.xlsx
+++ b/Planilhas_importação/Importacao_clientes.xlsx
@@ -212,8 +212,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Opcional. Informe o órgão emissor do documento de identificação cliente.
-Ex.: SSP</t>
+          <t xml:space="preserve">Informar BR ou UF.</t>
         </r>
       </text>
     </comment>
@@ -267,7 +266,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obrigatório. Informe o tipo de telefone para contato com o cliente:
+          <t xml:space="preserve">Opicional. Informe o tipo de telefone para contato com o cliente:
 - CELULAR
 - FIXO
 - COMERCIAL
@@ -283,9 +282,40 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obrigatório. Informar utilizando o padrão a seguir:
+          <t xml:space="preserve">Opicional.  Informar utilizando o padrão a seguir:
 Celular: 5573999341121
 Telefone fixo: 557330130001</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Opicional. Informe o tipo de telefone para contato com o cliente:
+- CELULAR
+- FIXO
+- COMERCIAL
+-RESIDENCIAL</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Opicional.  Informar utilizando o padrão a seguir:
+Celular: 5573999341121
+Telefone fixo: 557330130001
+</t>
         </r>
       </text>
     </comment>
@@ -1174,7 +1204,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="33">
+  <cellStyleXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1234,6 +1264,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
@@ -1247,7 +1280,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="32" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1272,7 +1305,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
@@ -1291,7 +1324,8 @@
     <cellStyle name="Normal" xfId="29"/>
     <cellStyle name="Título de tabela" xfId="30"/>
     <cellStyle name="Índice" xfId="31"/>
-    <cellStyle name="Destaque 3" xfId="32"/>
+    <cellStyle name="caption" xfId="32"/>
+    <cellStyle name="Destaque 3" xfId="33"/>
   </cellStyles>
   <colors>
     <indexedColors>
